--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118841265</v>
+        <v>118840019</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519085</v>
+        <v>519029</v>
       </c>
       <c r="R2" t="n">
-        <v>6582607</v>
+        <v>6582751</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118841641</v>
+        <v>118841922</v>
       </c>
       <c r="B3" t="n">
-        <v>57309</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,13 +854,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519064</v>
+        <v>519082</v>
       </c>
       <c r="R3" t="n">
-        <v>6582815</v>
+        <v>6582693</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118841922</v>
+        <v>118841641</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>57309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +942,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519082</v>
+        <v>519064</v>
       </c>
       <c r="R4" t="n">
-        <v>6582693</v>
+        <v>6582815</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,22 +1009,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1044,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118840019</v>
+        <v>118841265</v>
       </c>
       <c r="B5" t="n">
-        <v>57659</v>
+        <v>57831</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,16 +1071,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1088,11 +1093,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519029</v>
+        <v>519085</v>
       </c>
       <c r="R5" t="n">
-        <v>6582751</v>
+        <v>6582607</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -930,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118841641</v>
+        <v>118841265</v>
       </c>
       <c r="B4" t="n">
-        <v>57309</v>
+        <v>57831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519064</v>
+        <v>519085</v>
       </c>
       <c r="R4" t="n">
-        <v>6582815</v>
+        <v>6582607</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118841265</v>
+        <v>118841641</v>
       </c>
       <c r="B5" t="n">
-        <v>57831</v>
+        <v>57309</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,21 +1071,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519085</v>
+        <v>519064</v>
       </c>
       <c r="R5" t="n">
-        <v>6582607</v>
+        <v>6582815</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118840019</v>
+        <v>118841922</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519029</v>
+        <v>519082</v>
       </c>
       <c r="R2" t="n">
-        <v>6582751</v>
+        <v>6582693</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118841922</v>
+        <v>118841641</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>57309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519082</v>
+        <v>519064</v>
       </c>
       <c r="R3" t="n">
-        <v>6582693</v>
+        <v>6582815</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1055,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118841641</v>
+        <v>118840019</v>
       </c>
       <c r="B5" t="n">
-        <v>57309</v>
+        <v>57659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,21 +1066,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1093,6 +1088,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519064</v>
+        <v>519029</v>
       </c>
       <c r="R5" t="n">
-        <v>6582815</v>
+        <v>6582751</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118841922</v>
+        <v>118840019</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>57659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519082</v>
+        <v>519029</v>
       </c>
       <c r="R2" t="n">
-        <v>6582693</v>
+        <v>6582751</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118841641</v>
+        <v>118841265</v>
       </c>
       <c r="B3" t="n">
-        <v>57309</v>
+        <v>57831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519064</v>
+        <v>519085</v>
       </c>
       <c r="R3" t="n">
-        <v>6582815</v>
+        <v>6582607</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118841265</v>
+        <v>118841641</v>
       </c>
       <c r="B4" t="n">
-        <v>57831</v>
+        <v>57309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519085</v>
+        <v>519064</v>
       </c>
       <c r="R4" t="n">
-        <v>6582607</v>
+        <v>6582815</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118840019</v>
+        <v>118841922</v>
       </c>
       <c r="B5" t="n">
-        <v>57659</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,20 +1067,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1088,11 +1093,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519029</v>
+        <v>519082</v>
       </c>
       <c r="R5" t="n">
-        <v>6582751</v>
+        <v>6582693</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1134,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118841641</v>
+        <v>118841922</v>
       </c>
       <c r="B2" t="n">
-        <v>57311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519064</v>
+        <v>519082</v>
       </c>
       <c r="R2" t="n">
-        <v>6582815</v>
+        <v>6582693</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,37 +795,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118841922</v>
+        <v>118841641</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519082</v>
+        <v>519064</v>
       </c>
       <c r="R3" t="n">
-        <v>6582693</v>
+        <v>6582815</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Ola Erlandsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -928,16 +918,11 @@
         <v>118841265</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1050,32 +1035,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118840019</v>
+        <v>118841267</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1088,11 +1068,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1104,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519029</v>
+        <v>519011</v>
       </c>
       <c r="R5" t="n">
-        <v>6582751</v>
+        <v>6582868</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1144,135 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Aligh - Dylta bruk 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118840019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Halvarboda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519029</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6582751</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glanshammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Sara Poppelaars</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Aligh - Dylta bruk 1</t>
         </is>

--- a/artfynd/A 57553-2023 artfynd.xlsx
+++ b/artfynd/A 57553-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Aligh - Dylta bruk 1</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118841922</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Aligh - Dylta bruk 1</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118841641</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
           <t>Aligh - Dylta bruk 1</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118841265</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Aligh - Dylta bruk 1</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118841267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,8 +1302,20 @@
           <t>Aligh - Dylta bruk 1</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118840019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>